--- a/rosnedra_forecast/2026/rosnedra_page6.xlsx
+++ b/rosnedra_forecast/2026/rosnedra_page6.xlsx
@@ -416,12 +416,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="90" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -443,7 +443,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Извлекаемые запасы и природные ресурсы (с указанием категории) (ед.изм)</t>
+          <t>Извлекаемые запасы и прогнозные ресурсы</t>
         </is>
       </c>
     </row>
@@ -464,9 +464,9 @@
       <c r="D2" s="1" t="inlineStr">
         <is>
           <t>нефть (извл.):
-Dл - 512,4 млн т
+Dл - 138 млн.т.
 газ (извл.):
-Dл - 421,6 млрд м3</t>
+Dл - 299 млрд.м3</t>
         </is>
       </c>
     </row>
@@ -481,15 +481,15 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>Жиганский 3</t>
+          <t>Восточно-Линденский</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>нефть (извл.):
-Dл - 384,1 млн т
-газ (извл.):
-Dл - 305,2 млрд м3</t>
+          <t>газ (извл.):
+Dл - 781,5 млрд.м3;
+конденсат (извл.):
+Dл - 16,9 млн.т.</t>
         </is>
       </c>
     </row>
@@ -499,21 +499,20 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>Томская область</t>
+          <t>Республика Саха (Якутия)</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>Северо-Пудинский</t>
+          <t>Соболох-Маянский</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>нефть (геол./извл.):
-D1 - 4,382/1,406 млн т
-D2 - 1,228/0,393 млн т
-газ (геол./извл.):
-D1 - 0,842/0,842 млрд м3</t>
+          <t>газ (извл.):
+Dл - 798,7 млрд.м3;
+конденсат (извл.):
+Dл - 11,5 млн.т.</t>
         </is>
       </c>
     </row>
@@ -523,20 +522,18 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>Томская область</t>
+          <t>Республика Саха (Якутия)</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>Пудинский</t>
+          <t>Усть-Вилюйский</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>нефть (геол./извл.):
-D1 - 3,147/1,011 млн т
-газ (геол./извл.):
-D1 - 0,604/0,604 млрд м3</t>
+          <t>газ (извл.):
+C1 - 0,762 млрд.м3</t>
         </is>
       </c>
     </row>
@@ -546,20 +543,23 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>Томская область</t>
+          <t>Самарская область</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>Южно-Пудинский</t>
+          <t>Северо-Иргизский</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>нефть (геол./извл.):
-D1 - 2,904/0,933 млн т
-газ (геол./извл.):
-D1 - 0,557/0,557 млрд м3</t>
+          <t>нефть (извл.):
+D1 - 5,134 млн.т;
+D1(D3dm) - 8,9 млн.т.
+газ (извл.):
+D1 - 0,604 млрд. м3;
+конденсат (извл.):
+D1 - 0,01 млн.т</t>
         </is>
       </c>
     </row>
@@ -569,20 +569,19 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>Ханты-Мансийский автономный округ</t>
+          <t>Самарская область</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>Северо-Ляминский</t>
+          <t>Восточно-Каревский</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>нефть (извл.):
-C1 - 1,274 млн т
-газ (извл.):
-C1 - 0,118 млрд м3</t>
+          <t>нефть
+Dл - 11,058 млн.т
+D1(D3dm) - 12,96 млн.т</t>
         </is>
       </c>
     </row>
@@ -592,20 +591,20 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>Ханты-Мансийский автономный округ</t>
+          <t>Самарская область</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>Южно-Ляминский</t>
+          <t>Зеленогорский</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>нефть (извл.):
-C1 - 0,944 млн т
-газ (извл.):
-C1 - 0,086 млрд м3</t>
+          <t>нефть (геол./извл.)
+D0 - 4,901/1,934 млн.т.
+Dл - 4,876/1,881 млн.т.
+D1(D3dm) - 315,904/9,477 млн.т.</t>
         </is>
       </c>
     </row>
@@ -615,20 +614,88 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>Ямало-Ненецкий автономный округ</t>
+          <t>Саратовская область</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>Западно-Тамбейский</t>
+          <t>Гвардейский</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
+          <t>газ (геол./извл.):
+C1 - 0,5/0,5 млрд. м3
+C2 - 0,8/0,8 млрд. м3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>Саратовская область</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>Широко-Карамышский</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>нефть (извл.):
+B1 - 0,092 млн.т;
+газ (извл.):
+A - 0,468 млрд. м3;
+B1 - 0,612 млрд. м3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>Саратовская область</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>Смирновский</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
           <t>газ (извл.):
-C1 - 128,6 млрд м3
-конденсат (извл.):
-C1 - 7,42 млн т</t>
+C1 - 0,306 млрд. м3;
+C2 - 0,682 млрд. м3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>Саратовская область</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>Аряшский</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>нефть (извл.):
+C1 - 0,025 млн.т;
+газ (извл.):
+C1 - 0,028 млрд. м3</t>
         </is>
       </c>
     </row>
